--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.76994350870405</v>
+        <v>3.212615820164408</v>
       </c>
       <c r="D2" t="n">
-        <v>19.94611120719649</v>
+        <v>3.241243071169431</v>
       </c>
       <c r="E2" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F2" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.13111993628802</v>
+        <v>10.9088069896468</v>
       </c>
       <c r="D3" t="n">
-        <v>67.04798240735369</v>
+        <v>10.89529714119498</v>
       </c>
       <c r="E3" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F3" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.58159767509738</v>
+        <v>9.032009622203324</v>
       </c>
       <c r="D4" t="n">
-        <v>55.60104509850708</v>
+        <v>9.035169828507401</v>
       </c>
       <c r="E4" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F4" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.44283732041806</v>
+        <v>5.921961064567935</v>
       </c>
       <c r="D5" t="n">
-        <v>36.34838024195074</v>
+        <v>5.906611789316996</v>
       </c>
       <c r="E5" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F5" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.56789869276722</v>
+        <v>9.517283537574674</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64074362259754</v>
+        <v>9.529120838672101</v>
       </c>
       <c r="E6" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F6" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.68987614447759</v>
+        <v>9.537104873477608</v>
       </c>
       <c r="D7" t="n">
-        <v>58.84041146699389</v>
+        <v>9.561566863386508</v>
       </c>
       <c r="E7" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F7" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.437358229849962</v>
+        <v>0.7210707123506188</v>
       </c>
       <c r="D8" t="n">
-        <v>4.619781447432033</v>
+        <v>0.7507144852077055</v>
       </c>
       <c r="E8" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F8" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.24843772261998</v>
+        <v>2.477871129925747</v>
       </c>
       <c r="D9" t="n">
-        <v>15.41644814313279</v>
+        <v>2.505172823259078</v>
       </c>
       <c r="E9" t="n">
-        <v>22.27689113872157</v>
+        <v>3.619994810042256</v>
       </c>
       <c r="F9" t="n">
-        <v>22.21334735704111</v>
+        <v>3.609668945519181</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
